--- a/results/Int All Data -0.9/Rando_6_permute.xlsx
+++ b/results/Int All Data -0.9/Rando_6_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8997537732159533</v>
+        <v>0.876553583258175</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9020619996647804</v>
+        <v>0.876553583258175</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8960930952742017</v>
+        <v>0.8772300085401186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8960930952742017</v>
+        <v>0.8818464614377728</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8957349290850899</v>
+        <v>0.8813689730307843</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.889487074091515</v>
+        <v>0.8810108068416727</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.889487074091515</v>
+        <v>0.8814485876878626</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8757572371519103</v>
+        <v>0.8815282023449409</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8716581797575245</v>
+        <v>0.8819260760948512</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8716581797575245</v>
+        <v>0.8806528401880422</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8734887182638816</v>
+        <v>0.8839555514761634</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8750405057027241</v>
+        <v>0.8837566146012084</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8759160673951042</v>
+        <v>0.8794985274281473</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.887815565363833</v>
+        <v>0.8794985274281473</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.885706275789961</v>
+        <v>0.8690318937513468</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8847510994405026</v>
+        <v>0.8695889968154137</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8823632583345971</v>
+        <v>0.8697484256650518</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8868204819180947</v>
+        <v>0.8704252500179581</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8748816754595302</v>
+        <v>0.8684751897582428</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.880891085552833</v>
+        <v>0.868395774636646</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8801350456138111</v>
+        <v>0.8650527571812819</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8786227662002857</v>
+        <v>0.8650926642775618</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8757973437836717</v>
+        <v>0.8602772745049525</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8767924272294099</v>
+        <v>0.8140337294777757</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8792995905531922</v>
+        <v>0.8263704096862504</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8632621257712045</v>
+        <v>0.813953915285216</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8632621257712045</v>
+        <v>0.8134365197819475</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8632621257712045</v>
+        <v>0.8082629638202266</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8608345771045007</v>
+        <v>0.8045220726149525</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8608744842007805</v>
+        <v>0.7875292319480249</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8608744842007805</v>
+        <v>0.7971598119577623</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8648939269380882</v>
+        <v>0.7975179781468741</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8681174226400938</v>
+        <v>0.8031291154193039</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8721366658419201</v>
+        <v>0.8004230152205665</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.897366530716492</v>
+        <v>0.8032488367081434</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8942226496715646</v>
+        <v>0.804402949932557</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8930685364471511</v>
+        <v>0.8047611161216688</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8881336249211835</v>
+        <v>0.8095761068233154</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.888849957299407</v>
+        <v>0.8149885067562714</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.888849957299407</v>
+        <v>0.8125208514578062</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8881336249211835</v>
+        <v>0.8500492852639057</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8881336249211835</v>
+        <v>0.8394649256530797</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.839820896951896</v>
+        <v>0.8402209655921016</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8421291234007231</v>
+        <v>0.8396638625280347</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8313442306310908</v>
+        <v>0.8352461469698542</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8295533996855321</v>
+        <v>0.834171648402519</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.831980948352236</v>
+        <v>0.8309080460687519</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8325380514163029</v>
+        <v>0.8312662122578637</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8302695325282742</v>
+        <v>0.8199246154951274</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8288368677718272</v>
+        <v>0.7979168495741913</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8339707161727499</v>
+        <v>0.8012995745903536</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.816701319328603</v>
+        <v>0.8006231493084099</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8185318578349602</v>
+        <v>0.7940171281257233</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8195664493060156</v>
+        <v>0.7940171281257233</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8192082831169039</v>
+        <v>0.7832316367496468</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8163429536040099</v>
+        <v>0.7744363122650471</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.817059086446752</v>
+        <v>0.7737199798868235</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8332563791493404</v>
+        <v>0.7668749151974203</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8418122610562611</v>
+        <v>0.7723272222266564</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8424489787774062</v>
+        <v>0.7786548914127911</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.828361574255134</v>
+        <v>0.7774211635312991</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8288390626621226</v>
+        <v>0.7773413493387393</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.821437094444134</v>
+        <v>0.7699391815852694</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8127211850811311</v>
+        <v>0.7706158064026946</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7963646630643861</v>
+        <v>0.7606667677646439</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7991503779202018</v>
+        <v>0.7590351661332417</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7875693385797862</v>
+        <v>0.7598311131685436</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7794508384480928</v>
+        <v>0.7562494512774262</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7766252164959974</v>
+        <v>0.7617813729637404</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7209103207732399</v>
+        <v>0.7617813729637404</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.728989711950579</v>
+        <v>0.7617017583066621</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6546491767166037</v>
+        <v>0.7671536662649352</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6502715677901845</v>
+        <v>0.75823921909794</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6495552354119609</v>
+        <v>0.7329686489851626</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6321641219241605</v>
+        <v>0.7408483051456209</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6303732909786017</v>
+        <v>0.6828650900703164</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6505501193222178</v>
+        <v>0.689869384073876</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6502318602293859</v>
+        <v>0.6890337294777757</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.651346265893001</v>
+        <v>0.7147027719469076</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6472871155948952</v>
+        <v>0.7160947314651491</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6476452817840068</v>
+        <v>0.7140656551547996</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6494361127295656</v>
+        <v>0.6866460879073517</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6494361127295656</v>
+        <v>0.7041962311738273</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6491976678292934</v>
+        <v>0.7286704551803402</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.62444529136171</v>
+        <v>0.7069412407914375</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6210228587847491</v>
+        <v>0.7068618256698406</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6324045621792467</v>
+        <v>0.6915001875633525</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6086484663702899</v>
+        <v>0.7039970947633909</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6074139403468725</v>
+        <v>0.7026041375677423</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5545282582148757</v>
+        <v>0.6990623827729047</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5545282582148757</v>
+        <v>0.6282244933794128</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5663868514099177</v>
+        <v>0.6246823395136123</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5605372692372157</v>
+        <v>0.6243241733245006</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5546475804327525</v>
+        <v>0.6237273626996352</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5552842981538977</v>
+        <v>0.6172406637348253</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5564781189391098</v>
+        <v>0.5769686170594855</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5955158391265134</v>
+        <v>0.5769686170594855</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5976648362611839</v>
+        <v>0.5383648865441253</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.629223567534779</v>
+        <v>0.5298884197588015</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5327966494001963</v>
+        <v>0.5345445802172543</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5109104005874324</v>
+        <v>0.5434985354095665</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5093983207093885</v>
+        <v>0.5431403692204548</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.516483426582915</v>
+        <v>0.5337482341109896</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.541395032364655</v>
+        <v>0.5339072638896649</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5293758131070867</v>
+        <v>0.5241168559593267</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5127778531578485</v>
+        <v>0.5237983973310134</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5059728951002067</v>
+        <v>0.5343841536902092</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5123789817305313</v>
+        <v>0.5343045390331309</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5255108108323823</v>
+        <v>0.5192615590904375</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5179893208610356</v>
+        <v>0.5167549943730994</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5179893208610356</v>
+        <v>0.5239979328124127</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.52025724114262</v>
+        <v>0.5320374168934719</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5108649064976735</v>
+        <v>0.5320374168934719</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5084377569019323</v>
+        <v>0.5431006616596563</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5151231932062159</v>
+        <v>0.5430621513117463</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5020699810840363</v>
+        <v>0.5444948160681933</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5000407052382054</v>
+        <v>0.5227252955120479</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4989264991100718</v>
+        <v>0.5056514434396724</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4894553479499725</v>
+        <v>0.4982893823179638</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4894553479499725</v>
+        <v>0.4972148837506285</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4886993080109505</v>
+        <v>0.4887793217389916</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4916041455491615</v>
+        <v>0.4921618472196726</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5013929571956485</v>
+        <v>0.491246577966494</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5013929571956485</v>
+        <v>0.4899731425242037</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5012736349777718</v>
+        <v>0.5017128125723316</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5009551763494584</v>
+        <v>0.4992042525001796</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5023082264488271</v>
+        <v>0.4994033889106161</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5023082264488271</v>
+        <v>0.4968567175615168</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5023082264488271</v>
+        <v>0.4974537277218635</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.501870445602637</v>
+        <v>0.4974537277218635</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5025071633237822</v>
+        <v>0.4974537277218635</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5025071633237822</v>
+        <v>0.5016323997733276</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5021489971346705</v>
+        <v>0.5016323997733276</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5025071633237822</v>
+        <v>0.5026671907798644</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5021489971346705</v>
+        <v>0.5026671907798644</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5017908309455588</v>
+        <v>0.5008368518089886</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5022286117917488</v>
+        <v>0.5008368518089886</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5025867779808606</v>
+        <v>0.5025480680974691</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5018307380418386</v>
+        <v>0.5017523205976486</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5018307380418386</v>
+        <v>0.5026677893863086</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5018307380418386</v>
+        <v>0.5023094236617155</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5013532496348501</v>
+        <v>0.5023094236617155</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5013532496348501</v>
+        <v>0.5113040840922333</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5002787510675148</v>
+        <v>0.5078427420963996</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4999602924392015</v>
+        <v>0.5001215171081722</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4996817409071682</v>
+        <v>0.5015541818646192</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4994031893751347</v>
+        <v>0.4974940338891062</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5001195217533582</v>
+        <v>0.5013933562666113</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5005970101603467</v>
+        <v>0.5016719077986448</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5003581661891118</v>
+        <v>0.5011148047345779</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.5007566385454661</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.5007566385454661</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5003581661891118</v>
+        <v>0.4986479475780383</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5003581661891118</v>
+        <v>0.5029457423118979</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.5029457423118979</v>
       </c>
     </row>
   </sheetData>
